--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,40 +449,521 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>574</v>
+        <v>294.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2165</v>
+        <v>1253.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GROWW</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>1332.16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1233.57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FEDFINA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n">
+        <v>152.87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>712.62</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FIVESTAR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="n">
+        <v>463.87</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GOLDBEES</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>495</v>
+      </c>
+      <c r="C9" t="n">
+        <v>86.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GOLDCASE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>720</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.02</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1169.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C12" t="n">
+        <v>785.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>499.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>560</v>
+      </c>
+      <c r="C14" t="n">
+        <v>68.87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32</v>
+      </c>
+      <c r="C15" t="n">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>41</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1231.67</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>287</v>
+      </c>
+      <c r="C17" t="n">
+        <v>369.26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JAINREC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>318.79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JYOTHYLAB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>109</v>
+      </c>
+      <c r="C19" t="n">
+        <v>289.64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" t="n">
+        <v>359.15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>172</v>
+      </c>
+      <c r="C21" t="n">
+        <v>186.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" t="n">
+        <v>264.56</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MHRIL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>26</v>
+      </c>
+      <c r="C23" t="n">
+        <v>268.62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>170.38</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>43</v>
+      </c>
+      <c r="C25" t="n">
+        <v>863.85</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>281.48</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PHARMABEES</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>330</v>
+      </c>
+      <c r="C28" t="n">
+        <v>22.26</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SHARDACROP</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>858.3099999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SILVERBEES</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>60</v>
+      </c>
+      <c r="C30" t="n">
+        <v>124.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>760</v>
+      </c>
+      <c r="C31" t="n">
+        <v>29.85</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STOVEKRAFT</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>545.63</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STYL</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>45</v>
+      </c>
+      <c r="C33" t="n">
+        <v>404.33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>293</v>
+      </c>
+      <c r="C34" t="n">
+        <v>325.73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>20</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2521.56</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TEJASNET</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>613.59</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TMB</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>706.85</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>159</v>
+      </c>
+      <c r="C38" t="n">
+        <v>276.55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>161</v>
+      </c>
+      <c r="C39" t="n">
+        <v>424.93</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>77</v>
+      </c>
+      <c r="C40" t="n">
+        <v>225.33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>915.7</v>
       </c>
     </row>
   </sheetData>
